--- a/bankole_2026/documentation/tranD_sexBias_analysis.xlsx
+++ b/bankole_2026/documentation/tranD_sexBias_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ufgi$/SHARE/McIntyre_Lab/sex_specific_splicing/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C345F94-FCB9-2D47-A8A9-E52CA15648F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C182002B-E27B-F141-A864-B3A88E072CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>Project Name</t>
   </si>
@@ -47,123 +47,216 @@
     <t>Project Folder</t>
   </si>
   <si>
+    <t>Identify structural differences between transcripts that have one female and one male biased transcript</t>
+  </si>
+  <si>
+    <t>Scripts</t>
+  </si>
+  <si>
+    <t>SCRIPTS=PROJ/scripts</t>
+  </si>
+  <si>
+    <t>SCRIPTS=PROJ/sasprograms</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>brief description</t>
+  </si>
+  <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>submission script</t>
+  </si>
+  <si>
+    <t>input files</t>
+  </si>
+  <si>
+    <t>output files</t>
+  </si>
+  <si>
+    <t>Notes / results</t>
+  </si>
+  <si>
+    <t>mclab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identify the male/female biased  UJC in genes with sexBias=”both” </t>
+  </si>
+  <si>
+    <t>List of the genes with sex bias=”both”,  select all UJC in those genes, two datasets male biased and female biased</t>
+  </si>
+  <si>
+    <t>find_dmel_ujc_4_tranD.sas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dmel.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dmel.csv </t>
+  </si>
+  <si>
+    <t>dmel_male_ujc_4_TranD; dmel_female_ujc_4_TranD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">410 genes with sexBias in “both”  of these only 297 have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 550 male UJC and 715 female UJC </t>
+  </si>
+  <si>
+    <t>find_dsim_ujc_4_tranD.sas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dsim.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dsim.csv </t>
+  </si>
+  <si>
+    <t>dsim_male_ujc_4_TranD; dsim_female_ujc_4_TranD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">608 genes with sexBias in “both”  of these only 435  have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 874 male UJC and 1158 female UJC </t>
+  </si>
+  <si>
+    <t>find_dser_ujc_4_tranD.sas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dser.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dser.csv </t>
+  </si>
+  <si>
+    <t>dser_male_ujc_4_TranD; dser_female_ujc_4_TranD</t>
+  </si>
+  <si>
+    <t>493 genes with sexBias in “both”  of these only 327  have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 567  male UJC and 657 female UJC</t>
+  </si>
+  <si>
+    <t>dmel_data_2_dmel6_ujc_noMultiGene.gtf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gtf files in zenodo/datafiles </t>
+  </si>
+  <si>
+    <t>scp lists to hpg</t>
+  </si>
+  <si>
+    <t>scp gtfs to hpg</t>
+  </si>
+  <si>
+    <t>Deleted from hpg after subsetting</t>
+  </si>
+  <si>
+    <t>susbet gtfs for male biased and female biased transcripts</t>
+  </si>
+  <si>
+    <t>Run trand 2 gtf between M biased and F biased transcripts</t>
+  </si>
+  <si>
+    <t>hpg</t>
+  </si>
+  <si>
+    <t>Subset data gtfs for male biased and female biased transcripts in the lists above</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-PROJ=//SHARE/sex_specific_splicing/TranD_sexBias</t>
-  </si>
-  <si>
-    <t>Identify structural differences between transcripts that have one female and one male biased transcript</t>
-  </si>
-  <si>
-    <t>Scripts</t>
-  </si>
-  <si>
-    <t>SCRIPTS=PROJ/scripts</t>
-  </si>
-  <si>
-    <t>SCRIPTS=PROJ/sasprograms</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>brief description</t>
-  </si>
-  <si>
-    <t>program</t>
-  </si>
-  <si>
-    <t>submission script</t>
-  </si>
-  <si>
-    <t>input files</t>
-  </si>
-  <si>
-    <t>output files</t>
-  </si>
-  <si>
-    <t>Notes / results</t>
-  </si>
-  <si>
-    <t>mclab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">identify the male/female biased  UJC in genes with sexBias=”both” </t>
-  </si>
-  <si>
-    <t>List of the genes with sex bias=”both”,  select all UJC in those genes, two datasets male biased and female biased</t>
-  </si>
-  <si>
-    <t>find_dmel_ujc_4_tranD.sas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dmel.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dmel.csv </t>
-  </si>
-  <si>
-    <t>dmel_male_ujc_4_TranD; dmel_female_ujc_4_TranD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">410 genes with sexBias in “both”  of these only 297 have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 550 male UJC and 715 female UJC </t>
-  </si>
-  <si>
-    <t>find_dsim_ujc_4_tranD.sas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dsim.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dsim.csv </t>
-  </si>
-  <si>
-    <t>dsim_male_ujc_4_TranD; dsim_female_ujc_4_TranD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608 genes with sexBias in “both”  of these only 435  have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 874 male UJC and 1158 female UJC </t>
-  </si>
-  <si>
-    <t>find_dser_ujc_4_tranD.sas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/sex_specific_splicing/submission/supplementary_files/summary_files/gene_level_summary_from_dataFile_jxnHash_w_genesetid_dser.csv /mclab/SHARE/McIntyre_Lab/sex_specific_splicing/zenodo/datafiles/datafile_jxnHash_dser.csv </t>
-  </si>
-  <si>
-    <t>dser_male_ujc_4_TranD; dser_female_ujc_4_TranD</t>
-  </si>
-  <si>
-    <t>493 genes with sexBias in “both”  of these only 327  have UJC sig in both sexes the rest are a combination of UJC and ERP.  This is 567  male UJC and 657 female UJC</t>
-  </si>
-  <si>
-    <t>dmel_data_2_dmel6_ujc_noMultiGene.gtf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gtf files in zenodo/datafiles </t>
-  </si>
-  <si>
-    <t>scp lists to hpg</t>
-  </si>
-  <si>
-    <t>scp gtfs to hpg</t>
-  </si>
-  <si>
-    <t>Deleted from hpg after subsetting</t>
-  </si>
-  <si>
-    <t>susbet gtfs for male biased and female biased transcripts</t>
-  </si>
-  <si>
-    <t>Run trand 2 gtf between M biased and F biased transcripts</t>
-  </si>
-  <si>
-    <t>subset_M_F_bias_transcripts.sbatch</t>
-  </si>
-  <si>
-    <t>submit_trand_pairwise_M_vs_F_biased_ujcs.sbatch</t>
+PROJ=//SHARE/sex_specific_splicing/TranD_sexBias
+PORO (hpg) = /blue/mcintyre/share/sex_specific_splicing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${PROJ}/tand_sexBias/{species}_female_ujc_4_TranD.csv
+${PROJ}/trand_sexBias/{species}l_male_ujc_4_TranD.csv
+</t>
+  </si>
+  <si>
+    <t>${PROJ}/zenodo/datafiles/{species}_data_2_dser2_ujc_noMultiGene.gtf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+${PROJ}/TranD_sexBias/{species}_female_ujc_4_TranD.csv
+${PROJ}/TranD_sexBias/{species}l_male_ujc_4_TranD.csv
+</t>
+  </si>
+  <si>
+    <t>scp from share to hpg</t>
+  </si>
+  <si>
+    <t>${PROJ}/scripts/subset_M_F_bias_transcripts.sbatch</t>
+  </si>
+  <si>
+    <t>${PROJ}/scripts/submit_trand_pairwise_M_vs_F_biased_ujcs.sbatch</t>
+  </si>
+  <si>
+    <t>Using subset gtfs from above run TranD 2 gtf between male biased transcripts and female viased transcripts 
+see notes for TranD command</t>
+  </si>
+  <si>
+    <t>${PROJ}/{species}_data_2_dser2_ujc_noMultiGene.gtf</t>
+  </si>
+  <si>
+    <t>${PROJ}/scripts/subset_gtf_simple_03avn.py</t>
+  </si>
+  <si>
+    <t>export PATH=/blue/mcintyre/ammorse/conda_envs/trand_dev/bin:$PATH</t>
+  </si>
+  <si>
+    <t>${PROJ}/trand_sexBias/{species}_female_ujcs_4_TranD.gtf
+${PROJ}/trand_sexBias/{species}_male_ujcs_4_TranD.gtf</t>
+  </si>
+  <si>
+    <t>${PROJ}/scripts/ignore_AS_type_02ndk.py</t>
+  </si>
+  <si>
+    <t>Note: Updated column names in script from Kinfe's version (01ksb). TranD column names changed between
+e.g. num_diff_nt --&gt; num_nt_noOvlp</t>
+  </si>
+  <si>
+    <t>${PROJ}/run_plot_M_F_min_pair_upset.sbatch</t>
+  </si>
+  <si>
+    <t>${PROJ}/trand_sexBias/tranD_{species}_M_vs_F:</t>
+  </si>
+  <si>
+    <t>1. Subset pairwise_transcript distance.csv file to minimum distance (i.e. flag_min_match_dmel_male OR flag_min_match_dmel_female)
+2. Plot upset plot excluding 5, variation and 3' variation</t>
+  </si>
+  <si>
+    <t>Make custom TranD upset plots excluding 5' and 3' variation</t>
+  </si>
+  <si>
+    <t>${PROJ}/trand_sexBias/tranD_d${SPECIES}_M_vs_F
+/d${SPECIES}_male_vs_d${SPECIES}_female_minimum_pairwise_transcript_distance.csv</t>
+  </si>
+  <si>
+    <t>hpg 2 mclab</t>
+  </si>
+  <si>
+    <t>scp TranD output to mclab</t>
+  </si>
+  <si>
+    <t>${PROJ}/tranD_sexBias/tranD{species}_M_vs_F/custom_{species}_M_F_minimum_pairwise_distance_ignore_3_variation_ignore_5_variation_.png</t>
+  </si>
+  <si>
+    <t>trand \
+${IND}/d${SPECIES}_male_ujcs_4_TranD.gtf \
+${IND}/d${SPECIES}_female_ujcs_4_TranD.gtf \
+-o $OUTD \
+-1 d${SPECIES}_male \
+-2 d${SPECIES}_female \
+-f \
+-n $SLURM_CPUS_ON_NODE
+ERROR    | trand.minimum_distance:identify_min_pair:534 - Unexpected association of minimum distance within ties.</t>
+  </si>
+  <si>
+    <t>From HPG
+${PROJ}/tranD_sexBias/tranD{species}_M_vs_F:</t>
+  </si>
+  <si>
+    <t>To mclab
+${PROJ}/TranD_sexBias/tranD{species}_M_vs_F:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -200,8 +293,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,12 +310,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
         <bgColor rgb="FFCCFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,7 +343,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -450,13 +542,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.5" style="3"/>
     <col min="2" max="2" width="17.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="3"/>
+    <col min="4" max="4" width="20.83203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="21" style="3" customWidth="1"/>
     <col min="6" max="6" width="43.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="27.83203125" style="3" customWidth="1"/>
@@ -494,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -507,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -535,10 +627,10 @@
     </row>
     <row r="7" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -550,7 +642,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -570,116 +662,207 @@
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="70" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="70" x14ac:dyDescent="0.15">
       <c r="D13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="70" x14ac:dyDescent="0.15">
       <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="F16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="3" t="s">
+    </row>
+    <row r="18" spans="1:8" ht="112" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28" x14ac:dyDescent="0.15">
+      <c r="B20" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="6" t="s">
+    </row>
+    <row r="22" spans="1:8" ht="70" x14ac:dyDescent="0.15">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" s="6" customFormat="1" ht="42" x14ac:dyDescent="0.15">
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="255" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" s="6" customFormat="1" ht="56" x14ac:dyDescent="0.15">
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="98" x14ac:dyDescent="0.15">
+      <c r="A26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>39</v>
+      <c r="B26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="56" x14ac:dyDescent="0.15">
+      <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
